--- a/Pipeline_strain_comparison/assets/COMPARISON_strains_metadata.xlsx
+++ b/Pipeline_strain_comparison/assets/COMPARISON_strains_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\04_CNR_Legionella\Input_analysis_nextflow\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938696F6-6FD4-4788-BA0B-B9B71EC12A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB31DDD-506B-4DCD-A810-BB8D226A680A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B3C5F1E1-92BF-4413-A239-65E07C6C183A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3C5F1E1-92BF-4413-A239-65E07C6C183A}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -513,10 +513,10 @@
     </r>
   </si>
   <si>
-    <t>Origin : origine de l’échantillon. Valeurs autorisées : Clinic ou Environment (exactement ces termes).</t>
-  </si>
-  <si>
-    <t>Origin: sample source. Allowed values: Clinic or Environment (exact strings).</t>
+    <t>Origin : origine de l’échantillon. Valeurs autorisées : Clinical ou Environmental (exactement ces termes).</t>
+  </si>
+  <si>
+    <t>Origin: sample source. Allowed values: Clinical or Environmental (exact strings).</t>
   </si>
 </sst>
 </file>
@@ -1173,10 +1173,10 @@
       <c r="E20" s="3"/>
     </row>
   </sheetData>
-  <sheetProtection deleteRows="0"/>
+  <sheetProtection sheet="1" deleteRows="0"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong value" error="Veuillez choisir une valeur entre &quot;Clinic&quot; ou &quot;Environment&quot; seulement. _x000a_---_x000a_Please select either ‘Clinic’ or ‘Environment’ only. " sqref="D1:D1048576" xr:uid="{7781F29C-D146-4AD2-8551-C45AC2B371AA}">
-      <formula1>"Clinic,Environment"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong value" error="Veuillez choisir une valeur entre &quot;Clinical&quot; ou &quot;Environmental&quot; seulement. _x000a_---_x000a_Please select either ‘Clinical’ or ‘Environmental’ only. " sqref="D1:D1048576" xr:uid="{7781F29C-D146-4AD2-8551-C45AC2B371AA}">
+      <formula1>"Clinical,Environmental"</formula1>
     </dataValidation>
     <dataValidation type="whole" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong data format" error="Veuillez entrer l'année d'isolement/de récupération de l'échantillon au format YYYY._x000a_---_x000a_Please enter the year the sample was isolated/collected in the format YYYY." sqref="C1:C1048576" xr:uid="{5B5CF9F9-1897-4486-B33C-4A43570CE5F3}">
       <formula1>1900</formula1>
